--- a/order_forms/021_home_backup_generator_order_form--order_forms.xlsx
+++ b/order_forms/021_home_backup_generator_order_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -589,12 +589,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>backup_generator_select_form</t>
+          <t>backup_generator_select_form_2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Backup Generator</t>
+          <t>Backup Generator Select Form 2</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>power_select_form</t>
+          <t>power_select_form_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Power Select</t>
+          <t>Power Select Form 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -681,12 +681,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>features_select_form</t>
+          <t>features_select_form_2</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Features Select</t>
+          <t>Features Select Form 2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -732,7 +732,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Delivery Address</t>
+          <t>Delivery Address 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -1101,7 +1101,7 @@
   <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1160,7 +1160,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>backup_generator_select_form_choices</t>
+          <t>backup_generator_select_form_2_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1177,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>backup_generator_select_form_choices</t>
+          <t>backup_generator_select_form_2_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1228,51 +1228,51 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>power_select_form_choices</t>
+          <t>power_select_form_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>power_select_form_choices</t>
+          <t>power_select_form_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>power_select_form_choices</t>
+          <t>power_select_form_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>250</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1318,63 +1318,63 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>features_select_form_choices</t>
+          <t>features_select_form_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>features_select_form_choices</t>
+          <t>features_select_form_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>features_select_form_choices</t>
+          <t>features_select_form_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
